--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-medication-statement-document.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-medication-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,10 +85,9 @@
   </si>
   <si>
     <t xml:space="preserve">
- - L'entrée 'Traitement' est une entrée de type 'substanceAdministration' décrivant les modalités d'administration d'un médicament au patient.
- - Elle permet de décrire notamment le médicament, le mode d'administration, la quantité, la durée et la fréquence d'administration.
- - Si le traitement a déjà été administré ou si information rapporté par le patient ou si aucun traitement : 
-  • @moodCode='EVN'</t>
+ - FrMedicationStatementDocument permet de décrire les modalités d'administration d'un médicament au patient.
+ - Il permet de décrire notamment le médicament, le mode d'administration, la quantité, la durée et la fréquence d'administration.
+ - Si le traitement a déjà été administré ou si information rapporté par le patient ou si aucun traitement.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -398,7 +397,7 @@
 </t>
   </si>
   <si>
-    <t>Partie narrative de l’entrée</t>
+    <t>Partie narrative</t>
   </si>
   <si>
     <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
@@ -476,10 +475,10 @@
 </t>
   </si>
   <si>
-    <t>Fr Prescription</t>
-  </si>
-  <si>
-    <t>Instructions de prescription associées à l'administration du produit de santé.</t>
+    <t>Extension - Fr Prescription</t>
+  </si>
+  <si>
+    <t>Extension permettant d’indiquer les instructions de prescription associées à l'administration du produit de santé.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -496,10 +495,10 @@
 </t>
   </si>
   <si>
-    <t>Fr Précondition de l'administration</t>
-  </si>
-  <si>
-    <t>Lien vers la description narrative des conditions préalables dans le document CDA.</t>
+    <t>Extension - Fr Précondition de l'administration</t>
+  </si>
+  <si>
+    <t>Extension permettant d'indiquer le lien vers la description narrative des conditions préalables dans le document.</t>
   </si>
   <si>
     <t>MedicationStatement.modifierExtension</t>
@@ -532,7 +531,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant de l'entrée. L'entrée Traitement doit être identifiée de manière unique.</t>
+    <t>Identifiant. L'entrée Traitement doit être identifiée de manière unique.</t>
   </si>
   <si>
     <t>Identifiers associated with this Medication Statement that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -597,7 +596,7 @@
     <t>MedicationStatement.status</t>
   </si>
   <si>
-    <t>Statut de l’entrée</t>
+    <t>Statut</t>
   </si>
   <si>
     <t>A code representing the patient or other source's judgment about the state of the medication used that this statement is about.  Generally, this will be active or completed.</t>
@@ -865,7 +864,7 @@
     <t>MedicationStatement.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-condition|Observation)
 </t>
   </si>
   <si>
@@ -966,7 +965,7 @@
 </t>
   </si>
   <si>
-    <t>Fr Fréquence d’administration</t>
+    <t>Extension - Fr Fréquence d’administration</t>
   </si>
   <si>
     <t>Extension pour représenter la fréquence d'administration dans MedicationAdministration et MedicationStatement</t>
